--- a/sample-data/아이돌 출퇴근 정보/Samdeheon_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samdeheon_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R24e603f0da2b428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R6876b73a07ab4fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="R25b85cf6e7b9464c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Reaea7c65b5af40f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="Rae57281051ef4290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="R21811ad5129c403e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -35,8 +35,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1D252C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -46,6 +57,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0E6F5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -69,7 +90,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -87,6 +108,50 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -342,42 +407,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>멤버</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>상태</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="8" t="str">
         <x:v>원천ID</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="8" t="str">
         <x:v>비고</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="6" t="n">
+      <x:c r="A2" s="11" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="12" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="12" t="str">
         <x:v>출근</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>회사 입출 기록</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="12" t="str">
         <x:v>ATT-20260716-001</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="12" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
@@ -402,22 +467,22 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="6" t="n">
+      <x:c r="A4" s="11" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="12" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="12" t="str">
         <x:v>출근</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="12" t="str">
         <x:v>회사 입출 기록</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="12" t="str">
         <x:v>ATT-20260716-003</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="F4" s="12" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
@@ -442,22 +507,22 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="6" t="n">
+      <x:c r="A6" s="11" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="str">
+      <x:c r="B6" s="12" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
+      <x:c r="C6" s="12" t="str">
         <x:v>외부일정</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E6" s="3" t="str">
+      <x:c r="D6" s="12" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
         <x:v>CAL-20260718-001</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="F6" s="12" t="str">
         <x:v>음악방송 리허설</x:v>
       </x:c>
     </x:row>
@@ -482,22 +547,22 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="6" t="n">
+      <x:c r="A8" s="11" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="str">
+      <x:c r="B8" s="12" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="str">
+      <x:c r="C8" s="12" t="str">
         <x:v>외부일정</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E8" s="3" t="str">
+      <x:c r="D8" s="12" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="str">
         <x:v>CAL-20260718-001</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="F8" s="12" t="str">
         <x:v>음악방송 리허설</x:v>
       </x:c>
     </x:row>
@@ -522,22 +587,22 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="6" t="n">
+      <x:c r="A10" s="11" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B10" s="3" t="str">
+      <x:c r="B10" s="12" t="str">
         <x:v>장현우</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="str">
+      <x:c r="C10" s="12" t="str">
         <x:v>출근</x:v>
       </x:c>
-      <x:c r="D10" s="3" t="str">
+      <x:c r="D10" s="12" t="str">
         <x:v>회사 입출 기록</x:v>
       </x:c>
-      <x:c r="E10" s="3" t="str">
+      <x:c r="E10" s="12" t="str">
         <x:v>ATT-20260721-001</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
+      <x:c r="F10" s="12" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
@@ -562,62 +627,62 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="6" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B12" s="3" t="str">
+      <x:c r="A12" s="11" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C12" s="3" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D12" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E12" s="3" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
-      <x:c r="F12" s="3" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
+      <x:c r="C12" s="12" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="str">
+        <x:v>ATT-20260721-003</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
+        <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="6" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>이준영</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>ATT-20260721-004</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>라디오 스페셜 DJ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="11" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="B13" s="3" t="str">
-        <x:v>장현우</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="str">
+      <x:c r="B14" s="12" t="str">
+        <x:v>원준석</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
         <x:v>외부일정</x:v>
       </x:c>
-      <x:c r="D13" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="str">
+      <x:c r="D14" s="12" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E14" s="12" t="str">
         <x:v>CAL-20260725-001</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="6" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B14" s="3" t="str">
-        <x:v>김진현</x:v>
-      </x:c>
-      <x:c r="C14" s="3" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D14" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E14" s="3" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
-      <x:c r="F14" s="3" t="str">
+      <x:c r="F14" s="12" t="str">
         <x:v>팬미팅 무대 점검</x:v>
       </x:c>
     </x:row>
@@ -626,7 +691,7 @@
         <x:v>46228</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>이준영</x:v>
+        <x:v>장현우</x:v>
       </x:c>
       <x:c r="C15" s="3" t="str">
         <x:v>외부일정</x:v>
@@ -641,15 +706,58 @@
         <x:v>팬미팅 무대 점검</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="n">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>김진현</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>외부일정</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>CAL-20260725-001</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>팬미팅 무대 점검</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="15" t="n">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>이준영</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>외부일정</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="str">
+        <x:v>CAL-20260725-001</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="str">
+        <x:v>팬미팅 무대 점검</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="C2:C15">
       <x:formula1>"출근,대기,외부일정,제외"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C17">
+      <x:formula1>"출근,외부일정,제외"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c9512b454a24676"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b84accb9494c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -724,7 +832,7 @@
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>장현우, 김진현</x:v>
+        <x:v>원준석, 장현우, 김진현, 이준영</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
         <x:v>그룹 캘린더</x:v>
@@ -753,7 +861,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R575d37d9c8094022"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ecac57ffca94228"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -764,42 +872,63 @@
   <x:cols>
     <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="8" t="str">
+        <x:v>결제 시간</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
         <x:v>내역</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>금액</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="E1" s="22" t="str">
+        <x:v>예상 식사인원</x:v>
+      </x:c>
+      <x:c r="F1" s="23" t="str">
+        <x:v>정산 제외</x:v>
+      </x:c>
+      <x:c r="G1" s="18" t="str">
         <x:v>결제수단</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="H1" s="18" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="6" t="n">
+      <x:c r="A2" s="11" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="20" t="str">
+        <x:v>12:15</x:v>
+      </x:c>
+      <x:c r="C2" s="19" t="str">
         <x:v>합주실 점심</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="n">
+      <x:c r="D2" s="19" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="E2" s="24" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F2" s="25" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G2" s="13" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="H2" s="13" t="str">
         <x:v>PAY-20260716-001</x:v>
       </x:c>
     </x:row>
@@ -807,33 +936,51 @@
       <x:c r="A3" s="6" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="B3" s="21" t="str">
+        <x:v>11:40</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
         <x:v>방송국 도시락</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="n">
+      <x:c r="D3" s="7" t="n">
         <x:v>132000</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="E3" s="26" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F3" s="27" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>PAY-20260718-001</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="6" t="n">
+      <x:c r="A4" s="11" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="20" t="str">
+        <x:v>18:10</x:v>
+      </x:c>
+      <x:c r="C4" s="19" t="str">
         <x:v>라디오 대기 식사</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="n">
+      <x:c r="D4" s="19" t="n">
         <x:v>54000</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="E4" s="24" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F4" s="25" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G4" s="13" t="str">
         <x:v>배달앱</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="H4" s="13" t="str">
         <x:v>PAY-20260721-001</x:v>
       </x:c>
     </x:row>
@@ -841,23 +988,32 @@
       <x:c r="A5" s="6" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="str">
+      <x:c r="B5" s="21" t="str">
+        <x:v>19:05</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
         <x:v>팬미팅 리허설 저녁</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="n">
+      <x:c r="D5" s="7" t="n">
         <x:v>126000</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="E5" s="26" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F5" s="27" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>PAY-20260725-001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5caac0ccc4394458"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39e16791a12946fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/sample-data/아이돌 출퇴근 정보/Samdeheon_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samdeheon_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="Reaea7c65b5af40f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="Rae57281051ef4290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="R21811ad5129c403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R829e18856388480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R2bdf8e97d038427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rab669ab73fde4a4a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +46,20 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1D252C"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1D252C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -57,6 +69,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0E6F5"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -90,7 +112,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="50">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -152,6 +174,60 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -398,51 +474,51 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="30" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="30" t="str">
         <x:v>멤버</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="30" t="str">
         <x:v>상태</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="30" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="E1" s="30" t="str">
         <x:v>원천ID</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="F1" s="30" t="str">
         <x:v>비고</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="n">
+      <x:c r="A2" s="31" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="32" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D2" s="12" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="C2" s="32" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E2" s="32" t="str">
         <x:v>ATT-20260716-001</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="32" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
@@ -467,22 +543,22 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="11" t="n">
+      <x:c r="A4" s="31" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B4" s="12" t="str">
+      <x:c r="B4" s="32" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="C4" s="32" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E4" s="32" t="str">
         <x:v>ATT-20260716-003</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
+      <x:c r="F4" s="32" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
@@ -507,22 +583,22 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="11" t="n">
+      <x:c r="A6" s="31" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="str">
+      <x:c r="B6" s="32" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E6" s="12" t="str">
-        <x:v>CAL-20260718-001</x:v>
-      </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="C6" s="32" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E6" s="32" t="str">
+        <x:v>ATT-20260718-001</x:v>
+      </x:c>
+      <x:c r="F6" s="32" t="str">
         <x:v>음악방송 리허설</x:v>
       </x:c>
     </x:row>
@@ -534,35 +610,35 @@
         <x:v>장현우</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E7" s="3" t="str">
-        <x:v>CAL-20260718-001</x:v>
+        <x:v>ATT-20260718-002</x:v>
       </x:c>
       <x:c r="F7" s="3" t="str">
         <x:v>음악방송 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="11" t="n">
+      <x:c r="A8" s="31" t="n">
         <x:v>46221</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="str">
+      <x:c r="B8" s="32" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="str">
-        <x:v>CAL-20260718-001</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="str">
+      <x:c r="C8" s="32" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="str">
+        <x:v>ATT-20260718-003</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="str">
         <x:v>음악방송 리허설</x:v>
       </x:c>
     </x:row>
@@ -574,35 +650,35 @@
         <x:v>이준영</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>외부일정</x:v>
+        <x:v>출근</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
+        <x:v>회사 입출 기록</x:v>
       </x:c>
       <x:c r="E9" s="3" t="str">
-        <x:v>CAL-20260718-001</x:v>
+        <x:v>ATT-20260718-004</x:v>
       </x:c>
       <x:c r="F9" s="3" t="str">
         <x:v>음악방송 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="11" t="n">
+      <x:c r="A10" s="31" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
-        <x:v>장현우</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E10" s="12" t="str">
+      <x:c r="B10" s="32" t="str">
+        <x:v>원준석</x:v>
+      </x:c>
+      <x:c r="C10" s="32" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E10" s="32" t="str">
         <x:v>ATT-20260721-001</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
+      <x:c r="F10" s="32" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
@@ -611,7 +687,7 @@
         <x:v>46224</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
-        <x:v>김진현</x:v>
+        <x:v>장현우</x:v>
       </x:c>
       <x:c r="C11" s="3" t="str">
         <x:v>출근</x:v>
@@ -627,22 +703,22 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="11" t="n">
+      <x:c r="A12" s="31" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="str">
-        <x:v>원준석</x:v>
-      </x:c>
-      <x:c r="C12" s="12" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E12" s="12" t="str">
+      <x:c r="B12" s="32" t="str">
+        <x:v>김진현</x:v>
+      </x:c>
+      <x:c r="C12" s="32" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E12" s="32" t="str">
         <x:v>ATT-20260721-003</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="F12" s="32" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
@@ -667,97 +743,52 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="11" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B14" s="12" t="str">
-        <x:v>원준석</x:v>
-      </x:c>
-      <x:c r="C14" s="12" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E14" s="12" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
-      <x:c r="F14" s="12" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
-      </x:c>
+      <x:c r="A14" s="11"/>
+      <x:c r="B14" s="12"/>
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="12"/>
+      <x:c r="E14" s="12"/>
+      <x:c r="F14" s="12"/>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="6" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B15" s="3" t="str">
-        <x:v>장현우</x:v>
-      </x:c>
-      <x:c r="C15" s="3" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D15" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E15" s="3" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
-      <x:c r="F15" s="3" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
-      </x:c>
+      <x:c r="A15" s="6"/>
+      <x:c r="B15" s="3"/>
+      <x:c r="C15" s="3"/>
+      <x:c r="D15" s="3"/>
+      <x:c r="E15" s="3"/>
+      <x:c r="F15" s="3"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="14" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B16" s="13" t="str">
-        <x:v>김진현</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
-      </x:c>
+      <x:c r="A16" s="14"/>
+      <x:c r="B16" s="13"/>
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="13"/>
+      <x:c r="E16" s="13"/>
+      <x:c r="F16" s="13"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="15" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B17" s="10" t="str">
-        <x:v>이준영</x:v>
-      </x:c>
-      <x:c r="C17" s="10" t="str">
-        <x:v>외부일정</x:v>
-      </x:c>
-      <x:c r="D17" s="10" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E17" s="10" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
-      <x:c r="F17" s="10" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
-      </x:c>
+      <x:c r="A17" s="15"/>
+      <x:c r="B17" s="10"/>
+      <x:c r="C17" s="10"/>
+      <x:c r="D17" s="10"/>
+      <x:c r="E17" s="10"/>
+      <x:c r="F17" s="10"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="C2:C15">
       <x:formula1>"출근,대기,외부일정,제외"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="C2:C17">
       <x:formula1>"출근,외부일정,제외"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C13">
+      <x:formula1>"출근,외부일정,제외"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b84accb9494c59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3cd9c0c49b47b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -766,44 +797,44 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="30" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="30" t="str">
         <x:v>일정명</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="30" t="str">
         <x:v>참여 멤버</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="30" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="30" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="6" t="n">
+      <x:c r="A2" s="31" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="32" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="32" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="32" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="32" t="str">
         <x:v>CAL-20260716-001</x:v>
       </x:c>
     </x:row>
@@ -825,43 +856,33 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="6" t="n">
+      <x:c r="A4" s="31" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="32" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="32" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="32" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="32" t="str">
         <x:v>CAL-20260721-001</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="6" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="str">
-        <x:v>팬미팅 무대 점검</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="str">
-        <x:v>원준석, 장현우, 김진현, 이준영</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="str">
-        <x:v>그룹 캘린더</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="str">
-        <x:v>CAL-20260725-001</x:v>
-      </x:c>
+      <x:c r="A5" s="6"/>
+      <x:c r="B5" s="3"/>
+      <x:c r="C5" s="3"/>
+      <x:c r="D5" s="3"/>
+      <x:c r="E5" s="3"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ecac57ffca94228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd138085c5b1c445e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -870,65 +891,65 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="30" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="30" t="str">
         <x:v>결제 시간</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="30" t="str">
         <x:v>내역</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="30" t="str">
         <x:v>금액</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="str">
+      <x:c r="E1" s="39" t="str">
         <x:v>예상 식사인원</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="40" t="str">
         <x:v>정산 제외</x:v>
       </x:c>
-      <x:c r="G1" s="18" t="str">
+      <x:c r="G1" s="41" t="str">
         <x:v>결제수단</x:v>
       </x:c>
-      <x:c r="H1" s="18" t="str">
+      <x:c r="H1" s="41" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="11" t="n">
+      <x:c r="A2" s="31" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="20" t="str">
+      <x:c r="B2" s="42" t="str">
         <x:v>12:15</x:v>
       </x:c>
-      <x:c r="C2" s="19" t="str">
+      <x:c r="C2" s="43" t="str">
         <x:v>합주실 점심</x:v>
       </x:c>
-      <x:c r="D2" s="19" t="n">
+      <x:c r="D2" s="43" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="E2" s="24" t="str">
+      <x:c r="E2" s="44" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
       </x:c>
-      <x:c r="F2" s="25" t="str">
+      <x:c r="F2" s="45" t="str">
         <x:v>Manager Choi</x:v>
       </x:c>
-      <x:c r="G2" s="13" t="str">
+      <x:c r="G2" s="46" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H2" s="13" t="str">
+      <x:c r="H2" s="46" t="str">
         <x:v>PAY-20260716-001</x:v>
       </x:c>
     </x:row>
@@ -959,43 +980,43 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="11" t="n">
+      <x:c r="A4" s="31" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B4" s="20" t="str">
-        <x:v>18:10</x:v>
-      </x:c>
-      <x:c r="C4" s="19" t="str">
+      <x:c r="B4" s="42" t="str">
+        <x:v>12:05</x:v>
+      </x:c>
+      <x:c r="C4" s="43" t="str">
         <x:v>라디오 대기 식사</x:v>
       </x:c>
-      <x:c r="D4" s="19" t="n">
+      <x:c r="D4" s="43" t="n">
         <x:v>54000</x:v>
       </x:c>
-      <x:c r="E4" s="24" t="str">
+      <x:c r="E4" s="44" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
       </x:c>
-      <x:c r="F4" s="25" t="str">
+      <x:c r="F4" s="45" t="str">
         <x:v>Manager Choi</x:v>
       </x:c>
-      <x:c r="G4" s="13" t="str">
+      <x:c r="G4" s="46" t="str">
         <x:v>배달앱</x:v>
       </x:c>
-      <x:c r="H4" s="13" t="str">
+      <x:c r="H4" s="46" t="str">
         <x:v>PAY-20260721-001</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="6" t="n">
-        <x:v>46228</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
-        <x:v>19:05</x:v>
+        <x:v>12:30</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>팬미팅 리허설 저녁</x:v>
+        <x:v>라디오 추가 음료</x:v>
       </x:c>
       <x:c r="D5" s="7" t="n">
-        <x:v>126000</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="E5" s="26" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
@@ -1007,13 +1028,39 @@
         <x:v>법인카드</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>PAY-20260725-001</x:v>
+        <x:v>PAY-20260721-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="47" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="B6" s="49" t="str">
+        <x:v>12:50</x:v>
+      </x:c>
+      <x:c r="C6" s="46" t="str">
+        <x:v>라디오 간식 결제</x:v>
+      </x:c>
+      <x:c r="D6" s="48" t="n">
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="E6" s="45" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F6" s="45" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G6" s="46" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H6" s="46" t="str">
+        <x:v>PAY-20260721-003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39e16791a12946fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0a135de07ef44fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/sample-data/아이돌 출퇴근 정보/Samdeheon_external_activity_records.xlsx
+++ b/sample-data/아이돌 출퇴근 정보/Samdeheon_external_activity_records.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R829e18856388480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R2bdf8e97d038427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="Rab669ab73fde4a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="활동기록" sheetId="1" r:id="R0592af4f8c624cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정표" sheetId="2" r:id="R95726b088c9a44c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="결제내역" sheetId="3" r:id="R28c06b192742462d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -59,7 +59,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,6 +69,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F7A8C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0E6F5"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -112,7 +122,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="50">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -228,6 +238,24 @@
     <x:xf numFmtId="201" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -474,305 +502,353 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+      <x:c r="A1" s="51" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="30" t="str">
+      <x:c r="B1" s="51" t="str">
         <x:v>멤버</x:v>
       </x:c>
-      <x:c r="C1" s="30" t="str">
+      <x:c r="C1" s="51" t="str">
         <x:v>상태</x:v>
       </x:c>
-      <x:c r="D1" s="30" t="str">
+      <x:c r="D1" s="51" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="30" t="str">
+      <x:c r="E1" s="51" t="str">
         <x:v>원천ID</x:v>
       </x:c>
-      <x:c r="F1" s="30" t="str">
+      <x:c r="F1" s="51" t="str">
         <x:v>비고</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="31" t="n">
+      <x:c r="A2" s="52" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="32" t="str">
+      <x:c r="B2" s="53" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C2" s="32" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D2" s="32" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E2" s="32" t="str">
+      <x:c r="C2" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D2" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E2" s="53" t="str">
         <x:v>ATT-20260716-001</x:v>
       </x:c>
-      <x:c r="F2" s="32" t="str">
+      <x:c r="F2" s="53" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="6" t="n">
+      <x:c r="A3" s="15" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>장현우</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="C3" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
         <x:v>ATT-20260716-002</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="31" t="n">
+      <x:c r="A4" s="52" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B4" s="32" t="str">
+      <x:c r="B4" s="53" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C4" s="32" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D4" s="32" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E4" s="32" t="str">
+      <x:c r="C4" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D4" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E4" s="53" t="str">
         <x:v>ATT-20260716-003</x:v>
       </x:c>
-      <x:c r="F4" s="32" t="str">
+      <x:c r="F4" s="53" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="6" t="n">
+      <x:c r="A5" s="15" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>이준영</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="C5" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="str">
         <x:v>ATT-20260716-004</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="31" t="n">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="A6" s="52" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B6" s="53" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D6" s="32" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E6" s="32" t="str">
-        <x:v>ATT-20260718-001</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="str">
-        <x:v>음악방송 리허설</x:v>
+      <x:c r="C6" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D6" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E6" s="53" t="str">
+        <x:v>ATT-20260717-001</x:v>
+      </x:c>
+      <x:c r="F6" s="53" t="str">
+        <x:v>쇼케이스 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="6" t="n">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B7" s="3" t="str">
+      <x:c r="A7" s="15" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
         <x:v>장현우</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E7" s="3" t="str">
-        <x:v>ATT-20260718-002</x:v>
-      </x:c>
-      <x:c r="F7" s="3" t="str">
-        <x:v>음악방송 리허설</x:v>
+      <x:c r="C7" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="str">
+        <x:v>ATT-20260717-002</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="str">
+        <x:v>쇼케이스 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="31" t="n">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B8" s="32" t="str">
+      <x:c r="A8" s="52" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B8" s="53" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D8" s="32" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E8" s="32" t="str">
-        <x:v>ATT-20260718-003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="str">
-        <x:v>음악방송 리허설</x:v>
+      <x:c r="C8" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D8" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E8" s="53" t="str">
+        <x:v>ATT-20260717-003</x:v>
+      </x:c>
+      <x:c r="F8" s="53" t="str">
+        <x:v>쇼케이스 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="6" t="n">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B9" s="3" t="str">
+      <x:c r="A9" s="15" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
         <x:v>이준영</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D9" s="3" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E9" s="3" t="str">
-        <x:v>ATT-20260718-004</x:v>
-      </x:c>
-      <x:c r="F9" s="3" t="str">
-        <x:v>음악방송 리허설</x:v>
+      <x:c r="C9" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E9" s="10" t="str">
+        <x:v>ATT-20260717-004</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>쇼케이스 리허설</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="31" t="n">
+      <x:c r="A10" s="52" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B10" s="53" t="str">
+        <x:v>원준석</x:v>
+      </x:c>
+      <x:c r="C10" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D10" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E10" s="53" t="str">
+        <x:v>ATT-20260720-001</x:v>
+      </x:c>
+      <x:c r="F10" s="53" t="str">
+        <x:v>패션 광고 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="15" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>장현우</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E11" s="10" t="str">
+        <x:v>ATT-20260720-002</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
+        <x:v>패션 광고 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="52" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B12" s="53" t="str">
+        <x:v>김진현</x:v>
+      </x:c>
+      <x:c r="C12" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D12" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E12" s="53" t="str">
+        <x:v>ATT-20260720-003</x:v>
+      </x:c>
+      <x:c r="F12" s="53" t="str">
+        <x:v>패션 광고 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="15" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>이준영</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E13" s="10" t="str">
+        <x:v>ATT-20260720-004</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="str">
+        <x:v>패션 광고 촬영</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="52" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B10" s="32" t="str">
+      <x:c r="B14" s="53" t="str">
         <x:v>원준석</x:v>
       </x:c>
-      <x:c r="C10" s="32" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D10" s="32" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E10" s="32" t="str">
+      <x:c r="C14" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D14" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E14" s="53" t="str">
         <x:v>ATT-20260721-001</x:v>
       </x:c>
-      <x:c r="F10" s="32" t="str">
+      <x:c r="F14" s="53" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="22" customHeight="1">
-      <x:c r="A11" s="6" t="n">
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="15" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B11" s="3" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>장현우</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D11" s="3" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E11" s="3" t="str">
+      <x:c r="C15" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E15" s="10" t="str">
         <x:v>ATT-20260721-002</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="str">
+      <x:c r="F15" s="10" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="31" t="n">
+    <x:row r="16">
+      <x:c r="A16" s="52" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B12" s="32" t="str">
+      <x:c r="B16" s="53" t="str">
         <x:v>김진현</x:v>
       </x:c>
-      <x:c r="C12" s="32" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D12" s="32" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E12" s="32" t="str">
+      <x:c r="C16" s="53" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D16" s="53" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E16" s="53" t="str">
         <x:v>ATT-20260721-003</x:v>
       </x:c>
-      <x:c r="F12" s="32" t="str">
+      <x:c r="F16" s="53" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="6" t="n">
+    <x:row r="17">
+      <x:c r="A17" s="15" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B13" s="3" t="str">
+      <x:c r="B17" s="10" t="str">
         <x:v>이준영</x:v>
       </x:c>
-      <x:c r="C13" s="3" t="str">
-        <x:v>출근</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="str">
-        <x:v>회사 입출 기록</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="str">
+      <x:c r="C17" s="10" t="str">
+        <x:v>출근</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="str">
+        <x:v>회사 입출 기록</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="str">
         <x:v>ATT-20260721-004</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="str">
+      <x:c r="F17" s="10" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="11"/>
-      <x:c r="B14" s="12"/>
-      <x:c r="C14" s="12"/>
-      <x:c r="D14" s="12"/>
-      <x:c r="E14" s="12"/>
-      <x:c r="F14" s="12"/>
-    </x:row>
-    <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="6"/>
-      <x:c r="B15" s="3"/>
-      <x:c r="C15" s="3"/>
-      <x:c r="D15" s="3"/>
-      <x:c r="E15" s="3"/>
-      <x:c r="F15" s="3"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="14"/>
-      <x:c r="B16" s="13"/>
-      <x:c r="C16" s="13"/>
-      <x:c r="D16" s="13"/>
-      <x:c r="E16" s="13"/>
-      <x:c r="F16" s="13"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="15"/>
-      <x:c r="B17" s="10"/>
-      <x:c r="C17" s="10"/>
-      <x:c r="D17" s="10"/>
-      <x:c r="E17" s="10"/>
-      <x:c r="F17" s="10"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
@@ -788,7 +864,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3cd9c0c49b47b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0061815626f74d8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -797,92 +873,102 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+      <x:c r="A1" s="51" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="30" t="str">
+      <x:c r="B1" s="51" t="str">
         <x:v>일정명</x:v>
       </x:c>
-      <x:c r="C1" s="30" t="str">
+      <x:c r="C1" s="51" t="str">
         <x:v>참여 멤버</x:v>
       </x:c>
-      <x:c r="D1" s="30" t="str">
+      <x:c r="D1" s="51" t="str">
         <x:v>외부시스템</x:v>
       </x:c>
-      <x:c r="E1" s="30" t="str">
+      <x:c r="E1" s="51" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="31" t="n">
+      <x:c r="A2" s="52" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="32" t="str">
+      <x:c r="B2" s="53" t="str">
         <x:v>컴백 안무 합주</x:v>
       </x:c>
-      <x:c r="C2" s="32" t="str">
+      <x:c r="C2" s="53" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영</x:v>
       </x:c>
-      <x:c r="D2" s="32" t="str">
+      <x:c r="D2" s="53" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E2" s="32" t="str">
+      <x:c r="E2" s="53" t="str">
         <x:v>CAL-20260716-001</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="6" t="n">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="str">
-        <x:v>음악방송 리허설</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="A3" s="15" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>쇼케이스 리허설</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
-        <x:v>CAL-20260718-001</x:v>
+      <x:c r="E3" s="10" t="str">
+        <x:v>CAL-20260717-001</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="31" t="n">
+      <x:c r="A4" s="52" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B4" s="53" t="str">
+        <x:v>패션 광고 촬영</x:v>
+      </x:c>
+      <x:c r="C4" s="53" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영</x:v>
+      </x:c>
+      <x:c r="D4" s="53" t="str">
+        <x:v>그룹 캘린더</x:v>
+      </x:c>
+      <x:c r="E4" s="53" t="str">
+        <x:v>CAL-20260720-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="15" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B4" s="32" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>라디오 스페셜 DJ</x:v>
       </x:c>
-      <x:c r="C4" s="32" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영</x:v>
       </x:c>
-      <x:c r="D4" s="32" t="str">
+      <x:c r="D5" s="10" t="str">
         <x:v>그룹 캘린더</x:v>
       </x:c>
-      <x:c r="E4" s="32" t="str">
+      <x:c r="E5" s="10" t="str">
         <x:v>CAL-20260721-001</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="6"/>
-      <x:c r="B5" s="3"/>
-      <x:c r="C5" s="3"/>
-      <x:c r="D5" s="3"/>
-      <x:c r="E5" s="3"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd138085c5b1c445e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04577995795f450c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -891,82 +977,82 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14.25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="7.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+      <x:c r="A1" s="51" t="str">
         <x:v>날짜</x:v>
       </x:c>
-      <x:c r="B1" s="30" t="str">
+      <x:c r="B1" s="51" t="str">
         <x:v>결제 시간</x:v>
       </x:c>
-      <x:c r="C1" s="30" t="str">
+      <x:c r="C1" s="51" t="str">
         <x:v>내역</x:v>
       </x:c>
-      <x:c r="D1" s="30" t="str">
+      <x:c r="D1" s="51" t="str">
         <x:v>금액</x:v>
       </x:c>
-      <x:c r="E1" s="39" t="str">
+      <x:c r="E1" s="58" t="str">
         <x:v>예상 식사인원</x:v>
       </x:c>
-      <x:c r="F1" s="40" t="str">
+      <x:c r="F1" s="58" t="str">
         <x:v>정산 제외</x:v>
       </x:c>
-      <x:c r="G1" s="41" t="str">
+      <x:c r="G1" s="51" t="str">
         <x:v>결제수단</x:v>
       </x:c>
-      <x:c r="H1" s="41" t="str">
+      <x:c r="H1" s="51" t="str">
         <x:v>원천ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="31" t="n">
+      <x:c r="A2" s="52" t="n">
         <x:v>46219</x:v>
       </x:c>
-      <x:c r="B2" s="42" t="str">
+      <x:c r="B2" s="56" t="str">
         <x:v>12:15</x:v>
       </x:c>
-      <x:c r="C2" s="43" t="str">
+      <x:c r="C2" s="53" t="str">
         <x:v>합주실 점심</x:v>
       </x:c>
-      <x:c r="D2" s="43" t="n">
+      <x:c r="D2" s="54" t="n">
         <x:v>118000</x:v>
       </x:c>
-      <x:c r="E2" s="44" t="str">
+      <x:c r="E2" s="59" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
       </x:c>
-      <x:c r="F2" s="45" t="str">
+      <x:c r="F2" s="59" t="str">
         <x:v>Manager Choi</x:v>
       </x:c>
-      <x:c r="G2" s="46" t="str">
+      <x:c r="G2" s="53" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H2" s="46" t="str">
+      <x:c r="H2" s="53" t="str">
         <x:v>PAY-20260716-001</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="6" t="n">
-        <x:v>46221</x:v>
-      </x:c>
-      <x:c r="B3" s="21" t="str">
-        <x:v>11:40</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>방송국 도시락</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="n">
-        <x:v>132000</x:v>
-      </x:c>
-      <x:c r="E3" s="26" t="str">
+      <x:c r="A3" s="15" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="B3" s="57" t="str">
+        <x:v>18:10</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>쇼케이스 준비 저녁</x:v>
+      </x:c>
+      <x:c r="D3" s="55" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="E3" s="27" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
       </x:c>
       <x:c r="F3" s="27" t="str">
@@ -976,91 +1062,117 @@
         <x:v>법인카드</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>PAY-20260718-001</x:v>
+        <x:v>PAY-20260717-001</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="31" t="n">
+      <x:c r="A4" s="52" t="n">
+        <x:v>46223</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>12:20</x:v>
+      </x:c>
+      <x:c r="C4" s="53" t="str">
+        <x:v>광고 촬영 도시락</x:v>
+      </x:c>
+      <x:c r="D4" s="54" t="n">
+        <x:v>104000</x:v>
+      </x:c>
+      <x:c r="E4" s="59" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F4" s="59" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G4" s="53" t="str">
+        <x:v>법인카드</x:v>
+      </x:c>
+      <x:c r="H4" s="53" t="str">
+        <x:v>PAY-20260720-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="15" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B4" s="42" t="str">
+      <x:c r="B5" s="57" t="str">
         <x:v>12:05</x:v>
       </x:c>
-      <x:c r="C4" s="43" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>라디오 대기 식사</x:v>
       </x:c>
-      <x:c r="D4" s="43" t="n">
+      <x:c r="D5" s="55" t="n">
         <x:v>54000</x:v>
       </x:c>
-      <x:c r="E4" s="44" t="str">
-        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
-      </x:c>
-      <x:c r="F4" s="45" t="str">
-        <x:v>Manager Choi</x:v>
-      </x:c>
-      <x:c r="G4" s="46" t="str">
-        <x:v>배달앱</x:v>
-      </x:c>
-      <x:c r="H4" s="46" t="str">
-        <x:v>PAY-20260721-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="6" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="B5" s="21" t="str">
-        <x:v>12:30</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="str">
-        <x:v>라디오 추가 음료</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="n">
-        <x:v>24000</x:v>
-      </x:c>
-      <x:c r="E5" s="26" t="str">
+      <x:c r="E5" s="27" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
       </x:c>
       <x:c r="F5" s="27" t="str">
         <x:v>Manager Choi</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
+        <x:v>배달앱</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="str">
+        <x:v>PAY-20260721-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="52" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="B6" s="56" t="str">
+        <x:v>12:30</x:v>
+      </x:c>
+      <x:c r="C6" s="53" t="str">
+        <x:v>라디오 추가 음료</x:v>
+      </x:c>
+      <x:c r="D6" s="54" t="n">
+        <x:v>24000</x:v>
+      </x:c>
+      <x:c r="E6" s="59" t="str">
+        <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
+      </x:c>
+      <x:c r="F6" s="59" t="str">
+        <x:v>Manager Choi</x:v>
+      </x:c>
+      <x:c r="G6" s="53" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="H6" s="53" t="str">
         <x:v>PAY-20260721-002</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="47" t="n">
+    <x:row r="7">
+      <x:c r="A7" s="15" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="B6" s="49" t="str">
+      <x:c r="B7" s="57" t="str">
         <x:v>12:50</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>라디오 간식 결제</x:v>
       </x:c>
-      <x:c r="D6" s="48" t="n">
+      <x:c r="D7" s="55" t="n">
         <x:v>36000</x:v>
       </x:c>
-      <x:c r="E6" s="45" t="str">
+      <x:c r="E7" s="27" t="str">
         <x:v>원준석, 장현우, 김진현, 이준영, Manager Choi</x:v>
       </x:c>
-      <x:c r="F6" s="45" t="str">
+      <x:c r="F7" s="27" t="str">
         <x:v>Manager Choi</x:v>
       </x:c>
-      <x:c r="G6" s="46" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>법인카드</x:v>
       </x:c>
-      <x:c r="H6" s="46" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>PAY-20260721-003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0a135de07ef44fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4790a8c4881e4a89"/>
   </x:tableParts>
 </x:worksheet>
 </file>